--- a/data/MatrizSeguimientoEvaluacion_20260311_2127.xlsx
+++ b/data/MatrizSeguimientoEvaluacion_20260311_2127.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_7F7C4E8459B100A1C535B6B72639F598B53CF5BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C057296-1111-404D-BE07-5705710024B7}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_7F7C4E8459B100A1C535B6B72639F598B53CF5BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3526D047-9D5A-4195-B9D4-8F310D84FDF6}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId1"/>
@@ -2167,23 +2167,41 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2228,9 +2246,9 @@
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA SUSCRIPCION"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="FECHA DE CORTE GESPROY"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO" dataDxfId="2"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN" dataDxfId="0"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="FECHA DE CORTE GESPROY" dataDxfId="1"/>
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="INFORMACIÓN SOLICITADA"/>
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="INFORMACIÓN RECIBIDA"/>
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="FECHA DE RECIBO DE INFORMACIÓN"/>
@@ -2249,7 +2267,7 @@
     <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO"/>
     <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2614,75 +2632,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AV57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.7109375" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="39" width="25.7109375" customWidth="1"/>
-    <col min="40" max="40" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="41" max="45" width="25.7109375" customWidth="1"/>
-    <col min="46" max="46" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="47" max="48" width="25.7109375" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" customWidth="1"/>
+    <col min="5" max="39" width="25.6640625" customWidth="1"/>
+    <col min="40" max="40" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="41" max="45" width="25.6640625" customWidth="1"/>
+    <col min="46" max="46" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="47" max="48" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="7" t="s">
+    <row r="1" spans="1:48" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7"/>
-      <c r="AO1" s="7"/>
-      <c r="AP1" s="7"/>
-      <c r="AQ1" s="6" t="s">
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AR1" s="6"/>
-      <c r="AS1" s="6"/>
-      <c r="AT1" s="6"/>
-      <c r="AU1" s="6"/>
-      <c r="AV1" s="6"/>
-    </row>
-    <row r="2" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AR1" s="8"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+    </row>
+    <row r="2" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2828,8 +2846,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:48" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+    <row r="3" spans="1:48" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
         <v>2012000020041</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -2909,10 +2927,10 @@
       <c r="AB3" s="5">
         <v>41982</v>
       </c>
-      <c r="AC3" s="8">
+      <c r="AC3" s="6">
         <v>45260</v>
       </c>
-      <c r="AD3" s="3"/>
+      <c r="AD3" s="6"/>
       <c r="AE3" s="5">
         <v>46096</v>
       </c>
@@ -2957,7 +2975,7 @@
       </c>
       <c r="AV3" s="3"/>
     </row>
-    <row r="4" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2012000100008</v>
       </c>
@@ -3039,7 +3057,7 @@
         <v>41803</v>
       </c>
       <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
+      <c r="AD4" s="6"/>
       <c r="AE4" s="5">
         <v>46096</v>
       </c>
@@ -3082,7 +3100,7 @@
       </c>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>64</v>
       </c>
@@ -3158,7 +3176,7 @@
         <v>42038</v>
       </c>
       <c r="AC5" s="3"/>
-      <c r="AD5" s="3">
+      <c r="AD5" s="6">
         <v>45689</v>
       </c>
       <c r="AE5" s="5">
@@ -3203,7 +3221,7 @@
       </c>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>68</v>
       </c>
@@ -3278,10 +3296,10 @@
       <c r="AB6" s="5">
         <v>41586</v>
       </c>
-      <c r="AC6" s="8">
+      <c r="AC6" s="6">
         <v>46023</v>
       </c>
-      <c r="AD6" s="3"/>
+      <c r="AD6" s="6"/>
       <c r="AE6" s="5">
         <v>46096</v>
       </c>
@@ -3324,7 +3342,7 @@
       </c>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>71</v>
       </c>
@@ -3402,7 +3420,7 @@
       <c r="AC7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AD7" s="3"/>
+      <c r="AD7" s="6"/>
       <c r="AE7" s="5">
         <v>46096</v>
       </c>
@@ -3445,7 +3463,7 @@
       </c>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>78</v>
       </c>
@@ -3519,7 +3537,7 @@
         <v>43280</v>
       </c>
       <c r="AC8" s="3"/>
-      <c r="AD8" s="3">
+      <c r="AD8" s="6">
         <v>45797</v>
       </c>
       <c r="AE8" s="5">
@@ -3564,7 +3582,7 @@
       </c>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>80</v>
       </c>
@@ -3640,7 +3658,7 @@
         <v>43591</v>
       </c>
       <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
+      <c r="AD9" s="6"/>
       <c r="AE9" s="5">
         <v>46096</v>
       </c>
@@ -3683,7 +3701,7 @@
       </c>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>82</v>
       </c>
@@ -3759,7 +3777,7 @@
         <v>43908</v>
       </c>
       <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
+      <c r="AD10" s="6"/>
       <c r="AE10" s="5">
         <v>46096</v>
       </c>
@@ -3802,7 +3820,7 @@
       </c>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>85</v>
       </c>
@@ -3878,7 +3896,7 @@
         <v>43543</v>
       </c>
       <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
+      <c r="AD11" s="6"/>
       <c r="AE11" s="5">
         <v>46096</v>
       </c>
@@ -3921,7 +3939,7 @@
       </c>
       <c r="AV11" s="3"/>
     </row>
-    <row r="12" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>87</v>
       </c>
@@ -3995,7 +4013,7 @@
         <v>43781</v>
       </c>
       <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
+      <c r="AD12" s="6"/>
       <c r="AE12" s="5">
         <v>46096</v>
       </c>
@@ -4038,7 +4056,7 @@
       </c>
       <c r="AV12" s="3"/>
     </row>
-    <row r="13" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>89</v>
       </c>
@@ -4116,7 +4134,7 @@
         <v>45301</v>
       </c>
       <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
+      <c r="AD13" s="6"/>
       <c r="AE13" s="5">
         <v>46096</v>
       </c>
@@ -4159,7 +4177,7 @@
       </c>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>94</v>
       </c>
@@ -4235,7 +4253,7 @@
         <v>44504</v>
       </c>
       <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
+      <c r="AD14" s="6"/>
       <c r="AE14" s="5">
         <v>46096</v>
       </c>
@@ -4278,7 +4296,7 @@
       </c>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>97</v>
       </c>
@@ -4354,7 +4372,7 @@
         <v>44545</v>
       </c>
       <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
+      <c r="AD15" s="6"/>
       <c r="AE15" s="5">
         <v>46096</v>
       </c>
@@ -4397,7 +4415,7 @@
       </c>
       <c r="AV15" s="3"/>
     </row>
-    <row r="16" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>100</v>
       </c>
@@ -4473,7 +4491,7 @@
         <v>44980</v>
       </c>
       <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
+      <c r="AD16" s="6"/>
       <c r="AE16" s="5">
         <v>46096</v>
       </c>
@@ -4516,7 +4534,7 @@
       </c>
       <c r="AV16" s="3"/>
     </row>
-    <row r="17" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>103</v>
       </c>
@@ -4594,7 +4612,7 @@
         <v>45469</v>
       </c>
       <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
+      <c r="AD17" s="6"/>
       <c r="AE17" s="5">
         <v>46096</v>
       </c>
@@ -4637,7 +4655,7 @@
       </c>
       <c r="AV17" s="3"/>
     </row>
-    <row r="18" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>106</v>
       </c>
@@ -4713,7 +4731,7 @@
         <v>44925</v>
       </c>
       <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
+      <c r="AD18" s="6"/>
       <c r="AE18" s="5">
         <v>46096</v>
       </c>
@@ -4756,7 +4774,7 @@
       </c>
       <c r="AV18" s="3"/>
     </row>
-    <row r="19" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>109</v>
       </c>
@@ -4832,7 +4850,7 @@
         <v>44925</v>
       </c>
       <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
+      <c r="AD19" s="6"/>
       <c r="AE19" s="5">
         <v>46096</v>
       </c>
@@ -4875,7 +4893,7 @@
       </c>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>111</v>
       </c>
@@ -4951,7 +4969,7 @@
         <v>44925</v>
       </c>
       <c r="AC20" s="3"/>
-      <c r="AD20" s="3"/>
+      <c r="AD20" s="6"/>
       <c r="AE20" s="5">
         <v>46096</v>
       </c>
@@ -4994,7 +5012,7 @@
       </c>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>113</v>
       </c>
@@ -5070,7 +5088,7 @@
         <v>44998</v>
       </c>
       <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
+      <c r="AD21" s="6"/>
       <c r="AE21" s="5">
         <v>46096</v>
       </c>
@@ -5113,7 +5131,7 @@
       </c>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>117</v>
       </c>
@@ -5189,7 +5207,7 @@
         <v>45714</v>
       </c>
       <c r="AC22" s="3"/>
-      <c r="AD22" s="3"/>
+      <c r="AD22" s="6"/>
       <c r="AE22" s="5">
         <v>46096</v>
       </c>
@@ -5232,7 +5250,7 @@
       </c>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>120</v>
       </c>
@@ -5308,7 +5326,7 @@
         <v>44869</v>
       </c>
       <c r="AC23" s="3"/>
-      <c r="AD23" s="3"/>
+      <c r="AD23" s="6"/>
       <c r="AE23" s="5">
         <v>46096</v>
       </c>
@@ -5351,7 +5369,7 @@
       </c>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>123</v>
       </c>
@@ -5425,7 +5443,7 @@
         <v>44495</v>
       </c>
       <c r="AC24" s="3"/>
-      <c r="AD24" s="3"/>
+      <c r="AD24" s="6"/>
       <c r="AE24" s="5">
         <v>46096</v>
       </c>
@@ -5468,7 +5486,7 @@
       </c>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>127</v>
       </c>
@@ -5544,7 +5562,7 @@
         <v>44698</v>
       </c>
       <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
+      <c r="AD25" s="6"/>
       <c r="AE25" s="5">
         <v>46096</v>
       </c>
@@ -5587,7 +5605,7 @@
       </c>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>130</v>
       </c>
@@ -5665,7 +5683,7 @@
         <v>45509</v>
       </c>
       <c r="AC26" s="3"/>
-      <c r="AD26" s="3"/>
+      <c r="AD26" s="6"/>
       <c r="AE26" s="5">
         <v>46096</v>
       </c>
@@ -5708,7 +5726,7 @@
       </c>
       <c r="AV26" s="3"/>
     </row>
-    <row r="27" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>132</v>
       </c>
@@ -5784,7 +5802,7 @@
         <v>45028</v>
       </c>
       <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
+      <c r="AD27" s="6"/>
       <c r="AE27" s="5">
         <v>46096</v>
       </c>
@@ -5827,7 +5845,7 @@
       </c>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>136</v>
       </c>
@@ -5901,7 +5919,7 @@
         <v>45139</v>
       </c>
       <c r="AC28" s="3"/>
-      <c r="AD28" s="3"/>
+      <c r="AD28" s="6"/>
       <c r="AE28" s="5">
         <v>46096</v>
       </c>
@@ -5944,7 +5962,7 @@
       </c>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>138</v>
       </c>
@@ -6020,7 +6038,7 @@
         <v>45111</v>
       </c>
       <c r="AC29" s="3"/>
-      <c r="AD29" s="3"/>
+      <c r="AD29" s="6"/>
       <c r="AE29" s="5">
         <v>46096</v>
       </c>
@@ -6063,7 +6081,7 @@
       </c>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>140</v>
       </c>
@@ -6139,7 +6157,7 @@
         <v>45112</v>
       </c>
       <c r="AC30" s="3"/>
-      <c r="AD30" s="3"/>
+      <c r="AD30" s="6"/>
       <c r="AE30" s="5">
         <v>46096</v>
       </c>
@@ -6182,7 +6200,7 @@
       </c>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>142</v>
       </c>
@@ -6258,7 +6276,7 @@
         <v>45426</v>
       </c>
       <c r="AC31" s="3"/>
-      <c r="AD31" s="3"/>
+      <c r="AD31" s="6"/>
       <c r="AE31" s="5">
         <v>46096</v>
       </c>
@@ -6301,7 +6319,7 @@
       </c>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>146</v>
       </c>
@@ -6379,7 +6397,7 @@
         <v>45847</v>
       </c>
       <c r="AC32" s="3"/>
-      <c r="AD32" s="3"/>
+      <c r="AD32" s="6"/>
       <c r="AE32" s="5">
         <v>46096</v>
       </c>
@@ -6422,7 +6440,7 @@
       </c>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>149</v>
       </c>
@@ -6500,7 +6518,7 @@
         <v>45202</v>
       </c>
       <c r="AC33" s="3"/>
-      <c r="AD33" s="3"/>
+      <c r="AD33" s="6"/>
       <c r="AE33" s="5">
         <v>46096</v>
       </c>
@@ -6543,7 +6561,7 @@
       </c>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>153</v>
       </c>
@@ -6621,7 +6639,7 @@
         <v>45411</v>
       </c>
       <c r="AC34" s="3"/>
-      <c r="AD34" s="3"/>
+      <c r="AD34" s="6"/>
       <c r="AE34" s="5">
         <v>46096</v>
       </c>
@@ -6664,7 +6682,7 @@
       </c>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>156</v>
       </c>
@@ -6738,7 +6756,7 @@
         <v>45223</v>
       </c>
       <c r="AC35" s="3"/>
-      <c r="AD35" s="3"/>
+      <c r="AD35" s="6"/>
       <c r="AE35" s="5">
         <v>46096</v>
       </c>
@@ -6781,7 +6799,7 @@
       </c>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>159</v>
       </c>
@@ -6855,7 +6873,7 @@
         <v>45967</v>
       </c>
       <c r="AC36" s="3"/>
-      <c r="AD36" s="3"/>
+      <c r="AD36" s="6"/>
       <c r="AE36" s="5">
         <v>46096</v>
       </c>
@@ -6898,7 +6916,7 @@
       </c>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>161</v>
       </c>
@@ -6976,7 +6994,7 @@
         <v>45440</v>
       </c>
       <c r="AC37" s="3"/>
-      <c r="AD37" s="3"/>
+      <c r="AD37" s="6"/>
       <c r="AE37" s="5">
         <v>46096</v>
       </c>
@@ -7019,7 +7037,7 @@
       </c>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>163</v>
       </c>
@@ -7095,7 +7113,7 @@
         <v>45616</v>
       </c>
       <c r="AC38" s="3"/>
-      <c r="AD38" s="3"/>
+      <c r="AD38" s="6"/>
       <c r="AE38" s="5">
         <v>46096</v>
       </c>
@@ -7138,7 +7156,7 @@
       </c>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>166</v>
       </c>
@@ -7216,7 +7234,7 @@
         <v>45580</v>
       </c>
       <c r="AC39" s="3"/>
-      <c r="AD39" s="3"/>
+      <c r="AD39" s="6"/>
       <c r="AE39" s="5">
         <v>46096</v>
       </c>
@@ -7259,7 +7277,7 @@
       </c>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>169</v>
       </c>
@@ -7337,7 +7355,7 @@
         <v>46006</v>
       </c>
       <c r="AC40" s="3"/>
-      <c r="AD40" s="3"/>
+      <c r="AD40" s="6"/>
       <c r="AE40" s="5">
         <v>46096</v>
       </c>
@@ -7380,7 +7398,7 @@
       </c>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>171</v>
       </c>
@@ -7458,7 +7476,7 @@
         <v>45793</v>
       </c>
       <c r="AC41" s="3"/>
-      <c r="AD41" s="3"/>
+      <c r="AD41" s="6"/>
       <c r="AE41" s="5">
         <v>46096</v>
       </c>
@@ -7501,7 +7519,7 @@
       </c>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>173</v>
       </c>
@@ -7577,7 +7595,7 @@
         <v>45869</v>
       </c>
       <c r="AC42" s="3"/>
-      <c r="AD42" s="3"/>
+      <c r="AD42" s="6"/>
       <c r="AE42" s="5">
         <v>46096</v>
       </c>
@@ -7620,7 +7638,7 @@
       </c>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>175</v>
       </c>
@@ -7686,7 +7704,7 @@
       <c r="AA43" s="5"/>
       <c r="AB43" s="5"/>
       <c r="AC43" s="3"/>
-      <c r="AD43" s="3"/>
+      <c r="AD43" s="6"/>
       <c r="AE43" s="5">
         <v>46096</v>
       </c>
@@ -7733,7 +7751,7 @@
       </c>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>178</v>
       </c>
@@ -7811,7 +7829,7 @@
         <v>45911</v>
       </c>
       <c r="AC44" s="3"/>
-      <c r="AD44" s="3"/>
+      <c r="AD44" s="6"/>
       <c r="AE44" s="5">
         <v>46096</v>
       </c>
@@ -7854,7 +7872,7 @@
       </c>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>180</v>
       </c>
@@ -7930,7 +7948,7 @@
         <v>45860</v>
       </c>
       <c r="AC45" s="3"/>
-      <c r="AD45" s="3"/>
+      <c r="AD45" s="6"/>
       <c r="AE45" s="5">
         <v>46096</v>
       </c>
@@ -7973,7 +7991,7 @@
       </c>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>185</v>
       </c>
@@ -8049,7 +8067,7 @@
         <v>45827</v>
       </c>
       <c r="AC46" s="3"/>
-      <c r="AD46" s="3"/>
+      <c r="AD46" s="6"/>
       <c r="AE46" s="5">
         <v>46096</v>
       </c>
@@ -8096,7 +8114,7 @@
       </c>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>190</v>
       </c>
@@ -8174,7 +8192,7 @@
         <v>45960</v>
       </c>
       <c r="AC47" s="3"/>
-      <c r="AD47" s="3"/>
+      <c r="AD47" s="6"/>
       <c r="AE47" s="5">
         <v>46096</v>
       </c>
@@ -8217,7 +8235,7 @@
       </c>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>192</v>
       </c>
@@ -8297,7 +8315,7 @@
         <v>45931</v>
       </c>
       <c r="AC48" s="3"/>
-      <c r="AD48" s="3"/>
+      <c r="AD48" s="6"/>
       <c r="AE48" s="5">
         <v>46096</v>
       </c>
@@ -8340,7 +8358,7 @@
       </c>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>196</v>
       </c>
@@ -8414,7 +8432,7 @@
       </c>
       <c r="AB49" s="5"/>
       <c r="AC49" s="3"/>
-      <c r="AD49" s="3"/>
+      <c r="AD49" s="6"/>
       <c r="AE49" s="5">
         <v>46096</v>
       </c>
@@ -8461,7 +8479,7 @@
       </c>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>198</v>
       </c>
@@ -8539,7 +8557,7 @@
         <v>46009</v>
       </c>
       <c r="AC50" s="3"/>
-      <c r="AD50" s="3"/>
+      <c r="AD50" s="6"/>
       <c r="AE50" s="5">
         <v>46096</v>
       </c>
@@ -8582,7 +8600,7 @@
       </c>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>200</v>
       </c>
@@ -8648,7 +8666,7 @@
       <c r="AA51" s="5"/>
       <c r="AB51" s="5"/>
       <c r="AC51" s="3"/>
-      <c r="AD51" s="3"/>
+      <c r="AD51" s="6"/>
       <c r="AE51" s="5">
         <v>46096</v>
       </c>
@@ -8695,7 +8713,7 @@
       </c>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>203</v>
       </c>
@@ -8753,7 +8771,7 @@
       <c r="AA52" s="5"/>
       <c r="AB52" s="5"/>
       <c r="AC52" s="3"/>
-      <c r="AD52" s="3"/>
+      <c r="AD52" s="6"/>
       <c r="AE52" s="5">
         <v>46096</v>
       </c>
@@ -8800,7 +8818,7 @@
       </c>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>205</v>
       </c>
@@ -8866,7 +8884,7 @@
       <c r="AA53" s="5"/>
       <c r="AB53" s="5"/>
       <c r="AC53" s="3"/>
-      <c r="AD53" s="3"/>
+      <c r="AD53" s="6"/>
       <c r="AE53" s="5">
         <v>46096</v>
       </c>
@@ -8913,7 +8931,7 @@
       </c>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>207</v>
       </c>
@@ -8987,7 +9005,7 @@
       </c>
       <c r="AB54" s="5"/>
       <c r="AC54" s="3"/>
-      <c r="AD54" s="3"/>
+      <c r="AD54" s="6"/>
       <c r="AE54" s="5">
         <v>46096</v>
       </c>
@@ -9034,7 +9052,7 @@
       </c>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>211</v>
       </c>
@@ -9102,7 +9120,7 @@
       <c r="AA55" s="5"/>
       <c r="AB55" s="5"/>
       <c r="AC55" s="3"/>
-      <c r="AD55" s="3"/>
+      <c r="AD55" s="6"/>
       <c r="AE55" s="5">
         <v>46096</v>
       </c>
@@ -9149,7 +9167,7 @@
       </c>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>215</v>
       </c>
@@ -9215,7 +9233,7 @@
       <c r="AA56" s="5"/>
       <c r="AB56" s="5"/>
       <c r="AC56" s="3"/>
-      <c r="AD56" s="3"/>
+      <c r="AD56" s="6"/>
       <c r="AE56" s="5">
         <v>46096</v>
       </c>
@@ -9262,7 +9280,7 @@
       </c>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>218</v>
       </c>
@@ -9320,7 +9338,7 @@
       <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
       <c r="AC57" s="3"/>
-      <c r="AD57" s="3"/>
+      <c r="AD57" s="6"/>
       <c r="AE57" s="5">
         <v>46096</v>
       </c>
@@ -9383,61 +9401,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="28" width="25.7109375" customWidth="1"/>
-    <col min="29" max="29" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="30" max="34" width="25.7109375" customWidth="1"/>
-    <col min="35" max="35" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="36" max="37" width="25.7109375" customWidth="1"/>
+    <col min="1" max="28" width="25.6640625" customWidth="1"/>
+    <col min="29" max="29" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="30" max="34" width="25.6640625" customWidth="1"/>
+    <col min="35" max="35" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="36" max="37" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="7" t="s">
+    <row r="1" spans="1:37" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="6" t="s">
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-    </row>
-    <row r="2" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="8"/>
+    </row>
+    <row r="2" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -9550,7 +9568,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>230</v>
       </c>
@@ -9629,7 +9647,7 @@
       </c>
       <c r="AK3" s="3"/>
     </row>
-    <row r="4" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>235</v>
       </c>
@@ -9708,7 +9726,7 @@
       </c>
       <c r="AK4" s="3"/>
     </row>
-    <row r="5" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>240</v>
       </c>
@@ -9791,7 +9809,7 @@
       </c>
       <c r="AK5" s="3"/>
     </row>
-    <row r="6" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>244</v>
       </c>
@@ -9874,7 +9892,7 @@
       </c>
       <c r="AK6" s="3"/>
     </row>
-    <row r="7" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>248</v>
       </c>
@@ -9953,7 +9971,7 @@
       </c>
       <c r="AK7" s="3"/>
     </row>
-    <row r="8" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>252</v>
       </c>
@@ -10032,7 +10050,7 @@
       </c>
       <c r="AK8" s="3"/>
     </row>
-    <row r="9" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>255</v>
       </c>
@@ -10111,7 +10129,7 @@
       </c>
       <c r="AK9" s="3"/>
     </row>
-    <row r="10" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>259</v>
       </c>
@@ -10190,7 +10208,7 @@
       </c>
       <c r="AK10" s="3"/>
     </row>
-    <row r="11" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>262</v>
       </c>
@@ -10269,7 +10287,7 @@
       </c>
       <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>265</v>
       </c>
@@ -10348,7 +10366,7 @@
       </c>
       <c r="AK12" s="3"/>
     </row>
-    <row r="13" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>269</v>
       </c>
@@ -10427,7 +10445,7 @@
       </c>
       <c r="AK13" s="3"/>
     </row>
-    <row r="14" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>272</v>
       </c>
@@ -10506,7 +10524,7 @@
       </c>
       <c r="AK14" s="3"/>
     </row>
-    <row r="15" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>275</v>
       </c>
@@ -10585,7 +10603,7 @@
       </c>
       <c r="AK15" s="3"/>
     </row>
-    <row r="16" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>278</v>
       </c>
@@ -10664,7 +10682,7 @@
       </c>
       <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>281</v>
       </c>
@@ -10759,34 +10777,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="18" width="25.7109375" customWidth="1"/>
+    <col min="1" max="18" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-    </row>
-    <row r="2" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+    </row>
+    <row r="2" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -10842,7 +10860,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>285</v>
       </c>
@@ -10882,7 +10900,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>289</v>
       </c>
@@ -10922,7 +10940,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>293</v>
       </c>
@@ -10962,7 +10980,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>297</v>
       </c>
@@ -11002,7 +11020,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>301</v>
       </c>
@@ -11042,7 +11060,7 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>305</v>
       </c>
@@ -11082,7 +11100,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>309</v>
       </c>
@@ -11122,7 +11140,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>314</v>
       </c>
@@ -11162,7 +11180,7 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>319</v>
       </c>
@@ -11202,7 +11220,7 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>323</v>
       </c>
@@ -11242,7 +11260,7 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>328</v>
       </c>
@@ -11282,7 +11300,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>333</v>
       </c>
@@ -11322,7 +11340,7 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>338</v>
       </c>
@@ -11362,7 +11380,7 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>342</v>
       </c>
@@ -11402,7 +11420,7 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>346</v>
       </c>
@@ -11442,7 +11460,7 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>350</v>
       </c>
@@ -11482,7 +11500,7 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>354</v>
       </c>
@@ -11522,7 +11540,7 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>358</v>
       </c>
@@ -11562,7 +11580,7 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>362</v>
       </c>
@@ -11602,7 +11620,7 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>366</v>
       </c>
@@ -11642,7 +11660,7 @@
       <c r="Q22" s="4"/>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>370</v>
       </c>
@@ -11682,7 +11700,7 @@
       <c r="Q23" s="4"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>374</v>
       </c>
@@ -11722,7 +11740,7 @@
       <c r="Q24" s="4"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>378</v>
       </c>
@@ -11762,7 +11780,7 @@
       <c r="Q25" s="4"/>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>382</v>
       </c>
@@ -11802,7 +11820,7 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>386</v>
       </c>
@@ -11842,7 +11860,7 @@
       <c r="Q27" s="4"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>390</v>
       </c>
@@ -11882,7 +11900,7 @@
       <c r="Q28" s="4"/>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>395</v>
       </c>
@@ -11922,7 +11940,7 @@
       <c r="Q29" s="4"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>399</v>
       </c>
@@ -11962,7 +11980,7 @@
       <c r="Q30" s="4"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>402</v>
       </c>
@@ -12002,7 +12020,7 @@
       <c r="Q31" s="4"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>407</v>
       </c>
@@ -12042,7 +12060,7 @@
       <c r="Q32" s="4"/>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>410</v>
       </c>
@@ -12082,7 +12100,7 @@
       <c r="Q33" s="4"/>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>413</v>
       </c>
@@ -12122,7 +12140,7 @@
       <c r="Q34" s="4"/>
       <c r="R34" s="3"/>
     </row>
-    <row r="35" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>416</v>
       </c>
@@ -12162,7 +12180,7 @@
       <c r="Q35" s="4"/>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>420</v>
       </c>
@@ -12202,7 +12220,7 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="3"/>
     </row>
-    <row r="37" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>424</v>
       </c>
@@ -12242,7 +12260,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>428</v>
       </c>
@@ -12282,7 +12300,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="3"/>
     </row>
-    <row r="39" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>432</v>
       </c>
@@ -12322,7 +12340,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>436</v>
       </c>
@@ -12362,7 +12380,7 @@
       <c r="Q40" s="4"/>
       <c r="R40" s="3"/>
     </row>
-    <row r="41" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>440</v>
       </c>
@@ -12402,7 +12420,7 @@
       <c r="Q41" s="4"/>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>443</v>
       </c>
@@ -12442,7 +12460,7 @@
       <c r="Q42" s="4"/>
       <c r="R42" s="3"/>
     </row>
-    <row r="43" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>446</v>
       </c>
@@ -12482,7 +12500,7 @@
       <c r="Q43" s="4"/>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>449</v>
       </c>
@@ -12522,7 +12540,7 @@
       <c r="Q44" s="4"/>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>452</v>
       </c>
@@ -12562,7 +12580,7 @@
       <c r="Q45" s="4"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>456</v>
       </c>
@@ -12602,7 +12620,7 @@
       <c r="Q46" s="4"/>
       <c r="R46" s="3"/>
     </row>
-    <row r="47" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>460</v>
       </c>
@@ -12642,7 +12660,7 @@
       <c r="Q47" s="4"/>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>463</v>
       </c>
@@ -12682,7 +12700,7 @@
       <c r="Q48" s="4"/>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>467</v>
       </c>
@@ -12722,7 +12740,7 @@
       <c r="Q49" s="4"/>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>470</v>
       </c>
@@ -12762,7 +12780,7 @@
       <c r="Q50" s="4"/>
       <c r="R50" s="3"/>
     </row>
-    <row r="51" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>473</v>
       </c>
@@ -12802,7 +12820,7 @@
       <c r="Q51" s="4"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>477</v>
       </c>
@@ -12842,7 +12860,7 @@
       <c r="Q52" s="4"/>
       <c r="R52" s="3"/>
     </row>
-    <row r="53" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>480</v>
       </c>
@@ -12882,7 +12900,7 @@
       <c r="Q53" s="4"/>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>483</v>
       </c>
@@ -12922,7 +12940,7 @@
       <c r="Q54" s="4"/>
       <c r="R54" s="3"/>
     </row>
-    <row r="55" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>486</v>
       </c>
@@ -12962,7 +12980,7 @@
       <c r="Q55" s="4"/>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>489</v>
       </c>
@@ -13002,7 +13020,7 @@
       <c r="Q56" s="4"/>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>492</v>
       </c>
@@ -13042,7 +13060,7 @@
       <c r="Q57" s="4"/>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>496</v>
       </c>
@@ -13082,7 +13100,7 @@
       <c r="Q58" s="4"/>
       <c r="R58" s="3"/>
     </row>
-    <row r="59" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>499</v>
       </c>
@@ -13122,7 +13140,7 @@
       <c r="Q59" s="4"/>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>502</v>
       </c>
@@ -13162,7 +13180,7 @@
       <c r="Q60" s="4"/>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>505</v>
       </c>
@@ -13202,7 +13220,7 @@
       <c r="Q61" s="4"/>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>509</v>
       </c>
@@ -13242,7 +13260,7 @@
       <c r="Q62" s="4"/>
       <c r="R62" s="3"/>
     </row>
-    <row r="63" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>512</v>
       </c>
@@ -13282,7 +13300,7 @@
       <c r="Q63" s="4"/>
       <c r="R63" s="3"/>
     </row>
-    <row r="64" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>516</v>
       </c>
@@ -13322,7 +13340,7 @@
       <c r="Q64" s="4"/>
       <c r="R64" s="3"/>
     </row>
-    <row r="65" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>520</v>
       </c>
@@ -13362,7 +13380,7 @@
       <c r="Q65" s="4"/>
       <c r="R65" s="3"/>
     </row>
-    <row r="66" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>523</v>
       </c>
@@ -13402,7 +13420,7 @@
       <c r="Q66" s="4"/>
       <c r="R66" s="3"/>
     </row>
-    <row r="67" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>526</v>
       </c>
@@ -13442,7 +13460,7 @@
       <c r="Q67" s="4"/>
       <c r="R67" s="3"/>
     </row>
-    <row r="68" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>529</v>
       </c>
@@ -13482,7 +13500,7 @@
       <c r="Q68" s="4"/>
       <c r="R68" s="3"/>
     </row>
-    <row r="69" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>532</v>
       </c>
@@ -13522,7 +13540,7 @@
       <c r="Q69" s="4"/>
       <c r="R69" s="3"/>
     </row>
-    <row r="70" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>535</v>
       </c>
@@ -13562,7 +13580,7 @@
       <c r="Q70" s="4"/>
       <c r="R70" s="3"/>
     </row>
-    <row r="71" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>539</v>
       </c>
@@ -13602,7 +13620,7 @@
       <c r="Q71" s="4"/>
       <c r="R71" s="3"/>
     </row>
-    <row r="72" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>542</v>
       </c>
@@ -13642,7 +13660,7 @@
       <c r="Q72" s="4"/>
       <c r="R72" s="3"/>
     </row>
-    <row r="73" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>545</v>
       </c>
@@ -13682,7 +13700,7 @@
       <c r="Q73" s="4"/>
       <c r="R73" s="3"/>
     </row>
-    <row r="74" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>548</v>
       </c>
@@ -13722,7 +13740,7 @@
       <c r="Q74" s="4"/>
       <c r="R74" s="3"/>
     </row>
-    <row r="75" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>551</v>
       </c>
@@ -13762,7 +13780,7 @@
       <c r="Q75" s="4"/>
       <c r="R75" s="3"/>
     </row>
-    <row r="76" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>554</v>
       </c>
@@ -13802,7 +13820,7 @@
       <c r="Q76" s="4"/>
       <c r="R76" s="3"/>
     </row>
-    <row r="77" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>557</v>
       </c>
@@ -13840,7 +13858,7 @@
       <c r="Q77" s="4"/>
       <c r="R77" s="3"/>
     </row>
-    <row r="78" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>561</v>
       </c>
@@ -13880,7 +13898,7 @@
       <c r="Q78" s="4"/>
       <c r="R78" s="3"/>
     </row>
-    <row r="79" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>565</v>
       </c>
@@ -13920,7 +13938,7 @@
       <c r="Q79" s="4"/>
       <c r="R79" s="3"/>
     </row>
-    <row r="80" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>569</v>
       </c>
@@ -13960,7 +13978,7 @@
       <c r="Q80" s="4"/>
       <c r="R80" s="3"/>
     </row>
-    <row r="81" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>573</v>
       </c>
@@ -14000,7 +14018,7 @@
       <c r="Q81" s="4"/>
       <c r="R81" s="3"/>
     </row>
-    <row r="82" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>576</v>
       </c>
@@ -14040,7 +14058,7 @@
       <c r="Q82" s="4"/>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>579</v>
       </c>
@@ -14080,7 +14098,7 @@
       <c r="Q83" s="4"/>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>583</v>
       </c>
@@ -14120,7 +14138,7 @@
       <c r="Q84" s="4"/>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>587</v>
       </c>
@@ -14160,7 +14178,7 @@
       <c r="Q85" s="4"/>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>591</v>
       </c>
@@ -14200,7 +14218,7 @@
       <c r="Q86" s="4"/>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>595</v>
       </c>
@@ -14240,7 +14258,7 @@
       <c r="Q87" s="4"/>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>599</v>
       </c>
@@ -14280,7 +14298,7 @@
       <c r="Q88" s="4"/>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>603</v>
       </c>
@@ -14320,7 +14338,7 @@
       <c r="Q89" s="4"/>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>608</v>
       </c>
@@ -14360,7 +14378,7 @@
       <c r="Q90" s="4"/>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>612</v>
       </c>
@@ -14400,7 +14418,7 @@
       <c r="Q91" s="4"/>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>615</v>
       </c>
@@ -14440,7 +14458,7 @@
       <c r="Q92" s="4"/>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>618</v>
       </c>
@@ -14478,7 +14496,7 @@
       <c r="Q93" s="4"/>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>620</v>
       </c>
@@ -14516,7 +14534,7 @@
       <c r="Q94" s="4"/>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>623</v>
       </c>
@@ -14556,7 +14574,7 @@
       <c r="Q95" s="4"/>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>627</v>
       </c>
@@ -14594,7 +14612,7 @@
       <c r="Q96" s="4"/>
       <c r="R96" s="3"/>
     </row>
-    <row r="97" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>630</v>
       </c>
@@ -14634,7 +14652,7 @@
       <c r="Q97" s="4"/>
       <c r="R97" s="3"/>
     </row>
-    <row r="98" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>634</v>
       </c>
@@ -14674,7 +14692,7 @@
       <c r="Q98" s="4"/>
       <c r="R98" s="3"/>
     </row>
-    <row r="99" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>638</v>
       </c>
@@ -14714,7 +14732,7 @@
       <c r="Q99" s="4"/>
       <c r="R99" s="3"/>
     </row>
-    <row r="100" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>641</v>
       </c>
@@ -14754,7 +14772,7 @@
       <c r="Q100" s="4"/>
       <c r="R100" s="3"/>
     </row>
-    <row r="101" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>645</v>
       </c>
@@ -14794,7 +14812,7 @@
       <c r="Q101" s="4"/>
       <c r="R101" s="3"/>
     </row>
-    <row r="102" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>649</v>
       </c>
@@ -14834,7 +14852,7 @@
       <c r="Q102" s="4"/>
       <c r="R102" s="3"/>
     </row>
-    <row r="103" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>653</v>
       </c>
@@ -14874,7 +14892,7 @@
       <c r="Q103" s="4"/>
       <c r="R103" s="3"/>
     </row>
-    <row r="104" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>656</v>
       </c>

--- a/data/MatrizSeguimientoEvaluacion_20260311_2127.xlsx
+++ b/data/MatrizSeguimientoEvaluacion_20260311_2127.xlsx
@@ -2185,14 +2185,14 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-    </dxf>
-    <dxf>
       <border outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -2247,8 +2247,8 @@
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA SUSCRIPCION"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO" dataDxfId="2"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN" dataDxfId="0"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="FECHA DE CORTE GESPROY" dataDxfId="1"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="FECHA DE CORTE GESPROY" dataDxfId="0"/>
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="INFORMACIÓN SOLICITADA"/>
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="INFORMACIÓN RECIBIDA"/>
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="FECHA DE RECIBO DE INFORMACIÓN"/>
@@ -14942,6 +14942,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -15085,22 +15100,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16FE95C2-8F95-4D67-8A20-916165236EF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9A1EF65-9D62-4CDA-B27D-0BB4F7C1A454}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7E85F87-9E09-42D9-BB06-BFE3FE303BD6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15116,21 +15133,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9A1EF65-9D62-4CDA-B27D-0BB4F7C1A454}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16FE95C2-8F95-4D67-8A20-916165236EF5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>